--- a/projects/bcms-linkage-v2/outputs/BCMS_연계성_V5.xlsx
+++ b/projects/bcms-linkage-v2/outputs/BCMS_연계성_V5.xlsx
@@ -19,12 +19,13 @@
     <sheet name="품질개념6" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="객체22" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="인용원문72" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="외부학술근거" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="온톨로지규칙" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="보류및누락" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="응답설계" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="검증계획" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="수정이력" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="배경인용18" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="외부학술근거" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="온톨로지규칙" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="보류및누락" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="응답설계" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="검증계획" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="수정이력" sheetId="18" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4214" uniqueCount="1782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4366" uniqueCount="1857">
   <si>
     <t xml:space="preserve">상태</t>
   </si>
@@ -55114,6 +55115,1709 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">원문</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">참고 번역</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연구자</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사용처</t>
+  </si>
+  <si>
+    <t xml:space="preserve">문자 대조</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abstract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Currently, a standardized process reference model specifically tailored for the business continuity management system (BCMS) is absent.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 특화된 표준화된 프로세스 참조모델은 존재하지 않는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">참조모델 부재</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문자 대조 일치 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-09</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moreover, BCMS processes have not been a primary focus of ongoing research endeavors.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">또한 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프로세스는 진행 중인 연구의 주된 초점이 아니었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프로세스 연구 부족</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Many organizations demonstrate a lack of preparedness and often fail to recognize the criticality of continuity</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">많은 조직이 대비 부족을 보이며 연속성의 중요성을 인식하지 못하는 경우가 많다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연속성 대비 부족</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the capability of an organization to sustain the delivery of products or services at acceptable predefined levels following a disruptive incident</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중단 사건 이후 허용 가능한 사전 정의 수준으로 제품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서비스 제공을 유지하는 조직의 능력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Arias</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ISO 22301·22313</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 인용한 업무연속성 정의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">업무연속성 정의</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It aims to strengthen the resilience of organizations to cyber threats and to optimize the processes for effective management within the disaster management cycle.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이는 사이버 위협에 대한 조직의 회복탄력성을 강화하고 재난관리 주기 안에서 효과적 관리를 위한 프로세스를 최적화하는 것을 목표로 한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복탄력성과 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프로세스</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">These requirements cover planning, implementation, operation, and ongoing monitoring and improvement of a process-driven BCMS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 요구사항은 프로세스 기반 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 계획</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">운영</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지속적 모니터링과 개선을 다룬다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(ISO 22301 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: BCMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 프로세스 기반</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As ISO 22301 is requirements-oriented and does not focus on the operation of a BCMS, it does not contain a process reference model of a BCMS.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ISO 22301</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">은 요구사항 중심이며 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 운영에 초점을 두지 않으므로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 프로세스 참조모델을 포함하지 않는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">표준은 요구사항 중심</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A60</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조직은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구사항에 대한 체크리스트 방식 수행에 어려움을 겪는 경우가 많은데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이것이 지속 가능하게 운영되는 경영시스템으로 반드시 이어지지 않기 때문이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">체크리스트식 접근의 한계</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlike information security management [13], no process reference model for business continuity management is derived from the agreed standards available.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정보보안관리와 달리 합의된 표준에서 도출된 업무연속성관리의 프로세스 참조모델은 없다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hence, the primary objective of this study is to develop a detailed yet generic BCMS core process reference model that is readily adaptable and implementable across all organizations.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">따라서 이 연구의 주된 목적은 모든 조직에 쉽게 적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이행할 수 있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상세하면서도 일반적인 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">핵심 프로세스 참조모델을 개발하는 것이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: Arias</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 목적</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A62</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">활동 수준의 입력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">출력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인터페이스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상호작용을 포함해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프로세스를 기술하는 상세 참조모델은 이 프로세스들의 최적 조정을 돕는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인터페이스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상호작용 기술의 가치</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A64</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 시범 적용의 핵심 발견은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 체계적 성격이 강화되었다는 점이며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, BCMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">틀 안의 프로세스와 역할 사이의 상호작용을 강조한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프로세스 간 상호작용의 중요성</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However, it is evident that an unaltered implementation of the reference model would be inadequate.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그러나 참조모델을 변경 없이 그대로 이행하는 것은 부적절할 것임이 분명하다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조직별 적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">평가 필요</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A method for determining the requisite capability or maturity level of BCMS processes may be employed within the BCMS framework to incorporate discussions on capability or maturity.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프로세스에 요구되는 역량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성숙 수준을 정하는 방법을 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">틀 안에서 사용하여 역량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성숙 논의를 포함할 수 있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">필요성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">후속 연구로 역량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성숙 논의 제시</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">B19</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 성격이 서로 다른 많은 프로세스를 포함하며</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이들은 복잡하게 상호 연관되어 있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프로세스 간 복잡한 상호 연관</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">B20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To ensure the system coherency and efficiency, business continuity managers should master many details of these processes.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시스템의 정합성과 효율을 보장하기 위해 업무연속성 관리자는 이 프로세스들의 많은 세부 사항을 숙지해야 한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시스템 정합성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(coherency)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">B21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One of the critical issues in the development of BCMS and the related supporting tools is the quality (adequacy, coherency, preciseness) of various kinds of knowledge embedded in them.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와 관련 지원 도구 개발의 핵심 쟁점 하나는 그 안에 담긴 여러 종류 지식의 품질</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적절성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정합성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정밀성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방법</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지식 품질과 온톨로지 접근</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">B23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If these threats occur, BCMS supports organizational resilience, capability for effective response and recovery.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이러한 위협이 발생하면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BCMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 조직의 회복탄력성과 효과적인 대응</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">복구 능력을 뒷받침한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배경</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: BCMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">와 조직 회복탄력성</t>
     </r>
   </si>
   <si>
@@ -69142,6 +70846,530 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFE8A317"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>1432</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>1437</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>1438</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>1442</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>1446</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>1449</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>1454</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>1457</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>1468</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>1474</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>1478</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>898</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>935</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>935</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>1491</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>935</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>1494</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>1495</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>935</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>1499</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F16"/>
@@ -69166,13 +71394,13 @@
         <v>877</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1425</v>
+        <v>1500</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1426</v>
+        <v>1501</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1427</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -69183,36 +71411,36 @@
         <v>953</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1428</v>
+        <v>1503</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1429</v>
+        <v>1504</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1430</v>
+        <v>1505</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1431</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>1432</v>
+        <v>1507</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>993</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1433</v>
+        <v>1508</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1434</v>
+        <v>1509</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1435</v>
+        <v>1510</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1436</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -69223,16 +71451,16 @@
         <v>958</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1428</v>
+        <v>1503</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1437</v>
+        <v>1512</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1438</v>
+        <v>1513</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1439</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -69243,36 +71471,36 @@
         <v>961</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1428</v>
+        <v>1503</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1440</v>
+        <v>1515</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1441</v>
+        <v>1516</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1442</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>1443</v>
+        <v>1518</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1444</v>
+        <v>1519</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1433</v>
+        <v>1508</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1434</v>
+        <v>1509</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1435</v>
+        <v>1510</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>1445</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -69283,16 +71511,16 @@
         <v>965</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1446</v>
+        <v>1521</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1447</v>
+        <v>1522</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1448</v>
+        <v>1523</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1449</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -69303,16 +71531,16 @@
         <v>969</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1450</v>
+        <v>1525</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1451</v>
+        <v>1526</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1452</v>
+        <v>1527</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>1453</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -69323,36 +71551,36 @@
         <v>999</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1454</v>
+        <v>1529</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1455</v>
+        <v>1530</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1456</v>
+        <v>1531</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1457</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>1458</v>
+        <v>1533</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>988</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1433</v>
+        <v>1508</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1434</v>
+        <v>1509</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1435</v>
+        <v>1510</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1459</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -69363,56 +71591,56 @@
         <v>974</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1428</v>
+        <v>1503</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1460</v>
+        <v>1535</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1461</v>
+        <v>1536</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1462</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>1463</v>
+        <v>1538</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>1003</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1464</v>
+        <v>1539</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1465</v>
+        <v>1540</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1466</v>
+        <v>1541</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1467</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>1468</v>
+        <v>1543</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>1007</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1464</v>
+        <v>1539</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1465</v>
+        <v>1540</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>1466</v>
+        <v>1541</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1467</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -69420,19 +71648,19 @@
         <v>924</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1469</v>
+        <v>1544</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1428</v>
+        <v>1503</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1470</v>
+        <v>1545</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1471</v>
+        <v>1546</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>1472</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -69443,16 +71671,16 @@
         <v>981</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1450</v>
+        <v>1525</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>1451</v>
+        <v>1526</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1473</v>
+        <v>1548</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1474</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -69460,257 +71688,19 @@
         <v>931</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1475</v>
+        <v>1550</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1428</v>
+        <v>1503</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1476</v>
+        <v>1551</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1477</v>
+        <v>1552</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>1478</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="100"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="72.21"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>1479</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1480</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1481</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1482</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1483</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>1484</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>1485</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>1486</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>1487</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>1491</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1493</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>1494</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>1495</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>1497</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>1498</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>1499</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1500</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1501</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>1502</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>1503</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>1504</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>1506</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>1509</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>1510</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>1511</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>1513</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>1514</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>1515</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>1516</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>1517</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>1518</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>1519</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>1521</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>1522</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1523</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>1524</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>1525</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>1527</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>1529</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1530</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>1531</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>1532</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>1533</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>1535</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>1536</v>
+        <v>1553</v>
       </c>
     </row>
   </sheetData>
@@ -69732,184 +71722,223 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="94.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="35.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="72.21"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
-        <v>1032</v>
+      <c r="A1" s="1" t="s">
+        <v>1554</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1537</v>
+        <v>1555</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1538</v>
+        <v>1556</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1539</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1540</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>1541</v>
+      <c r="A2" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1542</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1543</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1544</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1545</v>
+        <v>1558</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1560</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>1546</v>
+      <c r="A3" s="4" t="s">
+        <v>1561</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1547</v>
+        <v>1562</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1548</v>
+        <v>1563</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1549</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>1551</v>
+      <c r="A4" s="2" t="s">
+        <v>1565</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1552</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1553</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1554</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>1545</v>
+        <v>1566</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1568</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>1555</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>1556</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>1557</v>
+      <c r="A5" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1571</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1558</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>1545</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>1559</v>
+      <c r="A6" s="2" t="s">
+        <v>1573</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1560</v>
+        <v>1574</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1561</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>1563</v>
+        <v>1575</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1576</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>1564</v>
+      <c r="A7" s="4" t="s">
+        <v>1577</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1565</v>
+        <v>1578</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1566</v>
+        <v>1579</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1567</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>1563</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>1568</v>
+      <c r="A8" s="2" t="s">
+        <v>1581</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1570</v>
+        <v>1582</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1583</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1571</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1563</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>1572</v>
+      <c r="A9" s="4" t="s">
+        <v>1585</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1573</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>1574</v>
+        <v>1586</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1587</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1575</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>1563</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>1576</v>
+      <c r="A10" s="2" t="s">
+        <v>875</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1577</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1578</v>
+        <v>1589</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1590</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1579</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1580</v>
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>1611</v>
       </c>
     </row>
   </sheetData>
@@ -69931,122 +71960,184 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="127.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="43.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="94.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="35.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>1581</v>
+      <c r="A1" s="25" t="s">
+        <v>1032</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1582</v>
+        <v>1612</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1583</v>
+        <v>1613</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1615</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1584</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1585</v>
+      <c r="A2" s="3" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1617</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1586</v>
+        <v>1618</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1620</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1588</v>
+      <c r="A3" s="5" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1622</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1589</v>
+        <v>1623</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>1625</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>1590</v>
+      <c r="A4" s="3" t="s">
+        <v>1626</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1591</v>
+        <v>1627</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1592</v>
+        <v>1628</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1620</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>1593</v>
+      <c r="A5" s="5" t="s">
+        <v>1630</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1594</v>
+        <v>1631</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1595</v>
+        <v>1632</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1633</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>1620</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>1596</v>
+      <c r="A6" s="3" t="s">
+        <v>1634</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1597</v>
+        <v>1635</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1598</v>
+        <v>1636</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1637</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1638</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>1599</v>
+      <c r="A7" s="5" t="s">
+        <v>1639</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1600</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>1601</v>
+        <v>1640</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>1642</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>1638</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>1602</v>
+      <c r="A8" s="3" t="s">
+        <v>1643</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1603</v>
+        <v>1644</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1604</v>
+        <v>1645</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1646</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1638</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>1605</v>
+      <c r="A9" s="5" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>1648</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1606</v>
+        <v>1649</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>1650</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>1638</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>1607</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1608</v>
+      <c r="A10" s="3" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1652</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1609</v>
+        <v>1653</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1654</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1655</v>
       </c>
     </row>
   </sheetData>
@@ -70068,139 +72159,122 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="94.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="85.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="127.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
-        <v>1610</v>
+      <c r="A1" s="1" t="s">
+        <v>1656</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1611</v>
+        <v>1657</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1612</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1613</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>1614</v>
+      <c r="A2" s="2" t="s">
+        <v>1659</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1615</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>1616</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1617</v>
+        <v>1660</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1661</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>1618</v>
+      <c r="A3" s="4" t="s">
+        <v>1662</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1619</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>1620</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>1621</v>
+        <v>1663</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>1664</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>1622</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1623</v>
+      <c r="A4" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1666</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1624</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1625</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>1626</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>1627</v>
+      <c r="A5" s="4" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1669</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1628</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>1629</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>1630</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1631</v>
+      <c r="A6" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1672</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1632</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1633</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>1634</v>
+      <c r="A7" s="4" t="s">
+        <v>1674</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1635</v>
+        <v>1675</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1636</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>1637</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>1638</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1639</v>
+      <c r="A8" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1678</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1640</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>1641</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>1642</v>
+      <c r="A9" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1643</v>
+        <v>1680</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1644</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>1645</v>
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1684</v>
       </c>
     </row>
   </sheetData>
@@ -70222,6 +72296,160 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="94.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="85.56"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1691</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>1719</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -70238,16 +72466,16 @@
         <v>1032</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1646</v>
+        <v>1721</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1647</v>
+        <v>1722</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>1648</v>
+        <v>1723</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>1649</v>
+        <v>1724</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>875</v>
@@ -70255,479 +72483,479 @@
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>1650</v>
+        <v>1725</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1651</v>
+        <v>1726</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1652</v>
+        <v>1727</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1653</v>
+        <v>1728</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1654</v>
+        <v>1729</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1655</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>1656</v>
+        <v>1731</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1651</v>
+        <v>1726</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1657</v>
+        <v>1732</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1658</v>
+        <v>1733</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1659</v>
+        <v>1734</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1660</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>1661</v>
+        <v>1736</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1663</v>
+        <v>1738</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1664</v>
+        <v>1739</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1665</v>
+        <v>1740</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1666</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>1667</v>
+        <v>1742</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1668</v>
+        <v>1743</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1669</v>
+        <v>1744</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1670</v>
+        <v>1745</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1671</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>1672</v>
+        <v>1747</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1673</v>
+        <v>1748</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1674</v>
+        <v>1749</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1675</v>
+        <v>1750</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>1676</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>1677</v>
+        <v>1752</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1651</v>
+        <v>1726</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1678</v>
+        <v>1753</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1679</v>
+        <v>1754</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1680</v>
+        <v>1755</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1681</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>1682</v>
+        <v>1757</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1683</v>
+        <v>1758</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1684</v>
+        <v>1759</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1685</v>
+        <v>1760</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>1686</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>1687</v>
+        <v>1762</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1651</v>
+        <v>1726</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1688</v>
+        <v>1763</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1689</v>
+        <v>1764</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1690</v>
+        <v>1765</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1691</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>1692</v>
+        <v>1767</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1651</v>
+        <v>1726</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1693</v>
+        <v>1768</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1694</v>
+        <v>1769</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1695</v>
+        <v>1770</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1696</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>1697</v>
+        <v>1772</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1698</v>
+        <v>1773</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1699</v>
+        <v>1774</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>1700</v>
+        <v>1775</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1701</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>1702</v>
+        <v>1777</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1651</v>
+        <v>1726</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1703</v>
+        <v>1778</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1704</v>
+        <v>1779</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1705</v>
+        <v>1780</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1706</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>1707</v>
+        <v>1782</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1651</v>
+        <v>1726</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1708</v>
+        <v>1783</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1709</v>
+        <v>1784</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>1710</v>
+        <v>1785</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1660</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>1711</v>
+        <v>1786</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1712</v>
+        <v>1787</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1713</v>
+        <v>1788</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1714</v>
+        <v>1789</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1715</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>1716</v>
+        <v>1791</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1717</v>
+        <v>1792</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>1718</v>
+        <v>1793</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>1719</v>
+        <v>1794</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1720</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>1721</v>
+        <v>1796</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1722</v>
+        <v>1797</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1723</v>
+        <v>1798</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1724</v>
+        <v>1799</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>1725</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>1726</v>
+        <v>1801</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1727</v>
+        <v>1802</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1728</v>
+        <v>1803</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>1729</v>
+        <v>1804</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>1730</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>1731</v>
+        <v>1806</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1732</v>
+        <v>1807</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1733</v>
+        <v>1808</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1734</v>
+        <v>1809</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1735</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>1736</v>
+        <v>1811</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1737</v>
+        <v>1812</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1738</v>
+        <v>1813</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>1739</v>
+        <v>1814</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1740</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>1741</v>
+        <v>1816</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1742</v>
+        <v>1817</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1743</v>
+        <v>1818</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1744</v>
+        <v>1819</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1745</v>
+        <v>1820</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1746</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>1747</v>
+        <v>1822</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1742</v>
+        <v>1817</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1748</v>
+        <v>1823</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1749</v>
+        <v>1824</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>1750</v>
+        <v>1825</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>1751</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>1752</v>
+        <v>1827</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1753</v>
+        <v>1828</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1754</v>
+        <v>1829</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>1755</v>
+        <v>1830</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1756</v>
+        <v>1831</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>1757</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>1758</v>
+        <v>1833</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>1759</v>
+        <v>1834</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>1760</v>
+        <v>1835</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>1761</v>
+        <v>1836</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>1762</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>1763</v>
+        <v>1838</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1742</v>
+        <v>1817</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1764</v>
+        <v>1839</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>1765</v>
+        <v>1840</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>1766</v>
+        <v>1841</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>1767</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>1768</v>
+        <v>1843</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1742</v>
+        <v>1817</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>1769</v>
+        <v>1844</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>1770</v>
+        <v>1845</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>1771</v>
+        <v>1846</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>939</v>
@@ -70735,42 +72963,42 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>1772</v>
+        <v>1847</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1742</v>
+        <v>1817</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1773</v>
+        <v>1848</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>1774</v>
+        <v>1849</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>1775</v>
+        <v>1850</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>1776</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>1777</v>
+        <v>1852</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>1662</v>
+        <v>1737</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1778</v>
+        <v>1853</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>1779</v>
+        <v>1854</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>1780</v>
+        <v>1855</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>1781</v>
+        <v>1856</v>
       </c>
     </row>
   </sheetData>
